--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -18,7 +18,8 @@
     <sheet name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11_Documents" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.16</t>
+          <t>Application            app/PRAP.html v1.17</t>
         </is>
       </c>
     </row>
@@ -567,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-06</t>
+          <t>Generated              2026-08-07</t>
         </is>
       </c>
     </row>
@@ -648,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1001,7 +1002,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Prepare a workbook for someone to open in the application</t>
+          <t>Continue a plan somebody started inside the application</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1011,7 +1012,7 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>You have produced or edited data and the user wants to look at it.</t>
+          <t>The user hands you a workbook they built by typing into PRAP rather than one exported from a system of record.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1025,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Validate first. A file with errors still loads, but the user meets a findings report before they see any numbers.</t>
+          <t>Check the reference tables FIRST: python tools/prap_io.py to-json &lt;file.xlsx&gt; -o plan.prap.json, then look at PeriodWeightStandard and RoleFactor. A plan started blank seeds every one of them at 1.00 with a note saying so.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1038,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Deliver the .xlsx. Tell the user to open app/PRAP.html in a browser and drop the file on it - nothing is uploaded, and the application needs no network.</t>
+          <t>If they are still 1.00, say so before quoting any figure. The load formula then reduces to person_weight x month_coverage, which is a real number but not a resourced estimate.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1051,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Say what you changed, in rows: 'added 4 Assignment rows, 1 PersonPeriodWeight window' beats 'updated the plan'.</t>
+          <t>Offer to fill them in from whatever the user can tell you about their own standards, one (type, phase, period) at a time. Do not invent them.</t>
         </is>
       </c>
     </row>
@@ -1058,10 +1059,92 @@
       <c r="A32" s="8" t="inlineStr"/>
       <c r="B32" s="8" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Everything else is an ordinary workbook - the same schema, the same rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
           <t>do NOT</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>do not treat a seeded 1.00 as a measured value, and do not quietly replace it with a number of your own</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Prepare a workbook for someone to open in the application</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>when</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>You have produced or edited data and the user wants to look at it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr"/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Validate first. A file with errors still loads, but the user meets a findings report before they see any numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Deliver the .xlsx. Tell the user to open app/PRAP.html in a browser and drop the file on it - nothing is uploaded, and the application needs no network.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr"/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Say what you changed, in rows: 'added 4 Assignment rows, 1 PersonPeriodWeight window' beats 'updated the plan'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>do NOT</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>do not send a .prap.json to a person expecting a spreadsheet - convert it to .xlsx first, unless they asked for the JSON</t>
         </is>
@@ -1236,6 +1319,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>How a plan gets into the application</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>The second one changes what you may assume about a file you are handed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>load a file</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Drop a .xlsx workbook or a .prap.json file on the page. This is the path for anything you produce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>start blank</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>'Start blank' begins a plan with nothing in it but the standard value lists and settings, and opens every tab for typing. It is how someone plans from scratch without a workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>what blank contains</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>The Lists and Config sheets of the delivered template, plus a complete PeriodWeightStandard and RoleFactor grid built from those lists - every (type, phase, period) and (type, phase, period, role) combination, so nothing silently falls back to 1.00 and V-23 never fires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>placeholders</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Every seeded weight and role factor is 1.00 and says so in its note. They are NOT a company standard. If a user hands you a plan started this way, check whether those figures are still 1.00 before reading the FTE totals as real - until they are set, the load reduces to person_weight x month_coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>both end the same</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>A plan started blank exports to the same .xlsx and the same .prap.json as any other, so nothing downstream needs to know which way it began.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1277,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.18.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.19.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.17</t>
+          <t>Application            app/PRAP.html v1.18</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.19.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.20.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.18</t>
+          <t>Application            app/PRAP.html v1.19</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.20.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.21.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.19</t>
+          <t>Application            app/PRAP.html v1.20</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.21.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.22.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.20</t>
+          <t>Application            app/PRAP.html v1.21</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.22.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.23.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.21</t>
+          <t>Application            app/PRAP.html v1.22</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-07</t>
+          <t>Generated              2026-08-08</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.23.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.24.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.22</t>
+          <t>Application            app/PRAP.html v1.23</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.24.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.25.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.23</t>
+          <t>Application            app/PRAP.html v1.24</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.25.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.26.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.24</t>
+          <t>Application            app/PRAP.html v1.25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  5</t>
+          <t>Source schema version  6</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-08</t>
+          <t>Generated              2026-08-20</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.26.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.27.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.0.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.1.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.7.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.8.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.9.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.10.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.1.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.2.xlsx</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>project_type, clinical_phase, period_name</t>
+          <t>project_type, clinical_phase, work_scope_type, period_name</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>project_type, clinical_phase, period_name, role_name</t>
+          <t>project_type, clinical_phase, work_scope_type, period_name, role_name</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1924,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>'NewDrug CT', 'Biosimilar CT' or 'Others'. The first two are clinical trials.</t>
+          <t>'NewDrug CT', 'Biosimilar CT (Healthy)', 'Biosimilar CT (Patient)' or 'Others'. Everything but 'Others' is a clinical trial.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Required for either clinical trial type - with the type it selects the period weights.</t>
+          <t>Required for any clinical trial type - with the type and the work scope it selects the period weights.</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>outsourcing_type</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>outsourcing_type</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Full / Partial outsourcing, or Full In-house.</t>
+          <t>How much of the work is done in-house. With the type and phase it selects the standard weights and role factors.</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>EDC_setup</t>
+          <t>outsourcing_type</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>setup_party</t>
+          <t>outsourcing_type</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Who sets up EDC. Clinical trial types only.</t>
+          <t>Full / Partial outsourcing, or Full In-house. Descriptive - work_scope_type is what the weights are keyed on.</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>DataReviewSystem_setup</t>
+          <t>EDC_setup</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Who sets up the data review system.</t>
+          <t>Who sets up EDC. Clinical trial types only.</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>RBQM_setup</t>
+          <t>DataReviewSystem_setup</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Who sets up RBQM.</t>
+          <t>Who sets up the data review system.</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>DM_conduct</t>
+          <t>RBQM_setup</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Who reviews the data.</t>
+          <t>Who sets up RBQM.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>EDC_system</t>
+          <t>DM_conduct</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>EDC_system</t>
+          <t>setup_party</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>EDC system in use.</t>
+          <t>Who reviews the data.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>DataReviewSystem</t>
+          <t>EDC_system</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>DataReviewSystem</t>
+          <t>EDC_system</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Data review system in use.</t>
+          <t>EDC system in use.</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>RBQM_system</t>
+          <t>DataReviewSystem</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>RBQM_system</t>
+          <t>DataReviewSystem</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>RBQM system in use.</t>
+          <t>Data review system in use.</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>planned_member_count</t>
+          <t>RBQM_system</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -2406,10 +2406,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>RBQM_system</t>
+        </is>
+      </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Planned team size; compared against actual assignments.</t>
+          <t>RBQM system in use.</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2425,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>planned_member_count</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2437,7 +2441,7 @@
       <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Project start.</t>
+          <t>Planned team size; compared against actual assignments.</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2453,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -2465,7 +2469,7 @@
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Planned project end.</t>
+          <t>Project start.</t>
         </is>
       </c>
     </row>
@@ -2477,23 +2481,23 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>total_period_months</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>DERIVED - formula, do not type.</t>
+          <t>Planned project end.</t>
         </is>
       </c>
     </row>
@@ -2505,27 +2509,23 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>total_period_months</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>project_status</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Planned / Active / On hold / Completed.</t>
+          <t>DERIVED - formula, do not type.</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -2550,10 +2550,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Planned / Active / On hold / Completed.</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -2579,7 +2583,11 @@
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2589,7 +2597,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -2613,7 +2621,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>note_4</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -2637,7 +2645,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>note_5</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -2656,17 +2664,17 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Project</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2675,11 +2683,7 @@
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Foreign key to Project.</t>
-        </is>
-      </c>
+      <c r="F28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -2689,23 +2693,23 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>project_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>DERIVED - looked up from Project, do not type.</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -2717,27 +2721,23 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>milestone_name</t>
+          <t>project_name</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>milestone_name</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>From the standard list of ten. 'Inspection' may appear on several rows.</t>
+          <t>DERIVED - looked up from Project, do not type.</t>
         </is>
       </c>
     </row>
@@ -2749,12 +2749,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>milestone_date</t>
+          <t>milestone_name</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -2762,10 +2762,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>milestone_name</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Planned date.</t>
+          <t>From the standard list of ten. 'Inspection' may appear on several rows.</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2781,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>milestone_seq</t>
+          <t>milestone_date</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2793,7 +2797,7 @@
       <c r="E32" s="8" t="inlineStr"/>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Display order on the timeline.</t>
+          <t>Planned date.</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2809,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>milestone_seq</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -2821,24 +2825,24 @@
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. why a date moved, or which inspection body.</t>
+          <t>Display order on the timeline.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>ProjectPeriod</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -2849,7 +2853,7 @@
       <c r="E34" s="8" t="inlineStr"/>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>Free text. e.g. why a date moved, or which inspection body.</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2865,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -2877,7 +2881,7 @@
       <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>From the set for this project's type. UNIQUE within a project, so (project_id, period_name) is the key (R-11).</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2893,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>period_seq</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2905,7 +2909,7 @@
       <c r="E36" s="8" t="inlineStr"/>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Orders periods along the timeline. Unique within a project.</t>
+          <t>From the set for this project's type. UNIQUE within a project, so (project_id, period_name) is the key (R-11).</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2921,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>period_seq</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -2933,7 +2937,7 @@
       <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Inclusive.</t>
+          <t>Orders periods along the timeline. Unique within a project.</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2949,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -2961,7 +2965,7 @@
       <c r="E38" s="8" t="inlineStr"/>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Inclusive. Periods must not overlap or leave a gap.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2977,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -2989,7 +2993,7 @@
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Effort multiplier. Clinical trial types: seeded from PeriodWeightStandard. Others: type it.</t>
+          <t>Inclusive. Periods must not overlap or leave a gap.</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3005,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -3017,19 +3021,19 @@
       <c r="E40" s="8" t="inlineStr"/>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. why a derived date was overridden by hand.</t>
+          <t>Effort multiplier. Clinical trial types: seeded from PeriodWeightStandard. Others: type it.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>ProjectPeriod</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -3042,14 +3046,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
+      <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>'NewDrug CT' or 'Biosimilar CT'. 'Others' projects take manual weights instead.</t>
+          <t>Free text. e.g. why a derived date was overridden by hand.</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>The phase this standard applies to.</t>
+          <t>A clinical trial type. 'Others' projects take manual weights instead.</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>One of the seven clinical periods. Unique within a project (R-11).</t>
+          <t>The phase this standard applies to.</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -3138,10 +3138,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>work_scope_type</t>
+        </is>
+      </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. Default multiplier for this phase and period.</t>
+          <t>The work scope this standard applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3157,12 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -3166,27 +3170,31 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>period_name_clinical</t>
+        </is>
+      </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. the basis for this weight.</t>
+          <t>One of the seven clinical periods. Unique within a project (R-11).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>RoleFactor</t>
+          <t>PeriodWeightStandard</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3194,31 +3202,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
+      <c r="E46" s="8" t="inlineStr"/>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Which type's role list this row belongs to.</t>
+          <t>YOU SUPPLY. Default multiplier for this phase and period.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>RoleFactor</t>
+          <t>PeriodWeightStandard</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -3226,14 +3230,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>clinical_phase</t>
-        </is>
-      </c>
+      <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>The phase this factor applies to. Leave EMPTY for 'Others'.</t>
+          <t>Free text. e.g. the basis for this weight.</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -3258,10 +3258,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>project_type</t>
+        </is>
+      </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>The period this factor applies to.</t>
+          <t>Which type's role list this row belongs to.</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3277,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -3286,10 +3290,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>clinical_phase</t>
+        </is>
+      </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>The role.</t>
+          <t>The phase this factor applies to. Leave EMPTY for 'Others'.</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3309,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>role_factor</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3314,10 +3322,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr"/>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>work_scope_type</t>
+        </is>
+      </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. Relative burden of this role in this period.</t>
+          <t>The work scope this factor applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3341,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>role_note</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -3345,19 +3357,19 @@
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Basis for the factor.</t>
+          <t>The period this factor applies to.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>RoleFactor</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -3373,24 +3385,24 @@
       <c r="E52" s="8" t="inlineStr"/>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Unique key, e.g. PSN-001.</t>
+          <t>The role.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>RoleFactor</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>role_factor</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -3401,19 +3413,19 @@
       <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Display name.</t>
+          <t>YOU SUPPLY. Relative burden of this role in this period.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>RoleFactor</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>role_note</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -3429,7 +3441,7 @@
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Grouping for the dashboard.</t>
+          <t>Basis for the factor.</t>
         </is>
       </c>
     </row>
@@ -3441,12 +3453,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>primary_role</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -3457,7 +3469,7 @@
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Usual role; an assignment can override it.</t>
+          <t>Unique key, e.g. PSN-001.</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3481,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>capacity_fte</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -3485,7 +3497,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
+          <t>Display name.</t>
         </is>
       </c>
     </row>
@@ -3497,12 +3509,12 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>employment_start</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -3513,7 +3525,7 @@
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Blank = open.</t>
+          <t>Grouping for the dashboard.</t>
         </is>
       </c>
     </row>
@@ -3525,12 +3537,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>employment_end</t>
+          <t>primary_role</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -3541,7 +3553,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Blank = open.</t>
+          <t>Usual role; an assignment can override it.</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3565,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>capacity_fte</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -3569,7 +3581,7 @@
       <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3593,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>employment_start</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3595,7 +3607,11 @@
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="8" t="inlineStr"/>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Blank = open.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -3605,12 +3621,12 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>employment_end</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -3619,7 +3635,11 @@
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr"/>
-      <c r="F61" s="7" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Blank = open.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -3629,7 +3649,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>note_4</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -3643,7 +3663,11 @@
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="8" t="inlineStr"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -3653,7 +3677,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>note_5</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -3672,17 +3696,17 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3691,26 +3715,22 @@
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr"/>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>Unique key. One row per person + project + role.</t>
-        </is>
-      </c>
+      <c r="F64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3719,39 +3739,31 @@
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr"/>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Foreign key to Person.</t>
-        </is>
-      </c>
+      <c r="F65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>DERIVED - looked up from Person, do not type.</t>
-        </is>
-      </c>
+      <c r="F66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -3761,7 +3773,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -3777,7 +3789,7 @@
       <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>Unique key. One row per person + project + role.</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3801,12 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -3805,7 +3817,7 @@
       <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Must exist in RoleFactor for this project's type.</t>
+          <t>Foreign key to Person.</t>
         </is>
       </c>
     </row>
@@ -3817,23 +3829,23 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>assign_start_date</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Date the person joins the study.</t>
+          <t>DERIVED - looked up from Person, do not type.</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3857,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>assign_end_date</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3861,7 +3873,7 @@
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Date the person leaves. Blank = runs to project end.</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3885,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>person_weight</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -3889,7 +3901,7 @@
       <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>How much this person works on this project, e.g. 0.40.</t>
+          <t>Must exist in RoleFactor for this project's type.</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3913,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>assign_start_date</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3917,7 +3929,7 @@
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Date the person joins the study.</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3941,12 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>assign_end_date</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3943,7 +3955,11 @@
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr"/>
-      <c r="F73" s="7" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Date the person leaves. Blank = runs to project end.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -3953,7 +3969,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>person_weight</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -3967,22 +3983,26 @@
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr"/>
-      <c r="F74" s="8" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>How much this person works on this project, e.g. 0.40.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -3993,24 +4013,24 @@
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Foreign key to Assignment.</t>
+          <t>Free text.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -4019,26 +4039,22 @@
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Inclusive.</t>
-        </is>
-      </c>
+      <c r="F76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -4047,11 +4063,7 @@
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr"/>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>Inclusive. Windows within one assignment must not overlap.</t>
-        </is>
-      </c>
+      <c r="F77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -4061,12 +4073,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>weight_override</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -4077,7 +4089,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>REPLACES person_weight for these months - it does not multiply it.</t>
+          <t>Foreign key to Assignment.</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4101,12 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4105,24 +4117,24 @@
       <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Why the weight differs.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>list_name</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -4133,19 +4145,19 @@
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Which list this value belongs to.</t>
+          <t>Inclusive. Windows within one assignment must not overlap.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>weight_override</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4161,19 +4173,19 @@
       <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>A permitted value. Add a row inside the block to extend a list.</t>
+          <t>REPLACES person_weight for these months - it does not multiply it.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -4189,19 +4201,19 @@
       <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. when a value was added, or what it means.</t>
+          <t>Why the weight differs.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>list_name</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -4217,14 +4229,14 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Setting name.</t>
+          <t>Which list this value belongs to.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
@@ -4245,19 +4257,19 @@
       <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Setting value.</t>
+          <t>A permitted value. Add a row inside the block to extend a list.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -4272,6 +4284,90 @@
       </c>
       <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>Free text. e.g. when a value was added, or what it means.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Setting name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Setting value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr"/>
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>What it controls.</t>
         </is>
@@ -4291,7 +4387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4332,7 +4428,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>NewDrug CT, Biosimilar CT, Others</t>
+          <t>NewDrug CT, Biosimilar CT (Healthy), Biosimilar CT (Patient), Others</t>
         </is>
       </c>
     </row>
@@ -4351,130 +4447,142 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>outsourcing_type</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Full outsourcing, Partial outsourcing, Full In-house</t>
+          <t>fully in-housed, fully outsourced, Partially outsourced (in-house for EDC)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>setup_party</t>
+          <t>outsourcing_type</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>by CRO, by SB</t>
+          <t>Full outsourcing, Partial outsourcing, Full In-house</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>EDC_system</t>
+          <t>setup_party</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Veeva EDC, Rave, eSOURCE</t>
+          <t>by CRO, by SB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>DataReviewSystem</t>
+          <t>EDC_system</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Veeva DQS, Medidata CDS, No system (manual)</t>
+          <t>Veeva EDC, Rave, eSOURCE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>RBQM_system</t>
+          <t>DataReviewSystem</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>CluePoints, Medidata CDS, No system (manual)</t>
+          <t>Veeva DQS, Medidata CDS, No system (manual)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>RBQM_system</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Planned, Active, On hold, Completed</t>
+          <t>CluePoints, Medidata CDS, No system (manual)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>milestone_name</t>
+          <t>project_status</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Protocol (v1), CTA submission, FPI, First SIV, LPI, interim DB lock cut-off, interim DB lock, final DB lock cut-off, final DB lock, Inspection</t>
+          <t>Planned, Active, On hold, Completed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>milestone_name</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
+          <t>Protocol (v1), CTA submission, FPI, First SIV, LPI, interim DB lock cut-off, interim DB lock, final DB lock cut-off, final DB lock, Inspection</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>period_name_others</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Planning, Develop, Close</t>
+          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_others</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
+          <t>Planning, Develop, Close</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
           <t>role_others</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Project lead, Main staff, Other staff</t>
         </is>
@@ -4804,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5396,6 +5504,50 @@
       <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Error - an override on an assignment that does not exist is silently ignored, so the weight the user typed never applies and nothing says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>V-25</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>A project's work_scope_type does not contradict its outsourcing_type. The two unambiguous ends are checked: 'Full outsourcing' against 'fully outsourced', and 'Full In-house' against 'fully in-housed'.</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Warning - two columns on the same axis and only one of them drives the weights. A project marked 'Full In-house' and 'fully outsourced' is a slip, and the calculation would follow the field nobody was looking at. 'Partial outsourcing' is compatible with more than one scope and is not checked: a warning nobody can act on is a warning everybody learns to ignore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>V-26</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>No project carries a project_type that schema 6 retired - at present 'Biosimilar CT', which became 'Biosimilar CT (Healthy)' and 'Biosimilar CT (Patient)'.</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Error - reported as itself rather than as a generic unknown value, because the remedy is a choice the file cannot make on the user's behalf. Only they know whether the trial ran in healthy volunteers or in patients, and guessing would put a wrong weight on real work.</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5611,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.25</t>
+          <t>Application            app/PRAP.html v1.26</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-20</t>
+          <t>Generated              2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.27.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.28.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.1.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.2.xlsx</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5708,6 +5708,21 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Display unit: 'FTE' or 'percent'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>split_shared_role_fte</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1 = when several people hold the same role on one project in a month, the role factor is divided between them. 0 = each is charged the whole factor, which is how versions before this one behaved.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-24</t>
+          <t>Generated              2026-08-26</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.26</t>
+          <t>Application            app/PRAP.html v1.27</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.28.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.29.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.2.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.3.xlsx</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Date the person joins the study.</t>
+          <t>Date the person joins. BLANK = the project's own start date.</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Date the person leaves. Blank = runs to project end.</t>
+          <t>Date the person leaves. BLANK = the project's own end date.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.27</t>
+          <t>Application            app/PRAP.html v1.28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  6</t>
+          <t>Source schema version  7</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.29.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.30.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.3.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.4.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.8.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.9.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.10.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.11.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.2.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.3.xlsx</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>outsourcing_type</t>
+          <t>outsourcing_scope_det</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -2182,14 +2182,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>outsourcing_type</t>
-        </is>
-      </c>
+      <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Full / Partial outsourcing, or Full In-house. Descriptive - work_scope_type is what the weights are keyed on.</t>
+          <t>FREE TEXT. What is outsourced and to whom, in your own words - the detail behind work_scope_type. Read by people, never by the calculation.</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4459,130 +4455,118 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>outsourcing_type</t>
+          <t>setup_party</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Full outsourcing, Partial outsourcing, Full In-house</t>
+          <t>by CRO, by SB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>setup_party</t>
+          <t>EDC_system</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>by CRO, by SB</t>
+          <t>Veeva EDC, Rave, eSOURCE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>EDC_system</t>
+          <t>DataReviewSystem</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Veeva EDC, Rave, eSOURCE</t>
+          <t>Veeva DQS, Medidata CDS, No system (manual)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>DataReviewSystem</t>
+          <t>RBQM_system</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Veeva DQS, Medidata CDS, No system (manual)</t>
+          <t>CluePoints, Medidata CDS, No system (manual)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>RBQM_system</t>
+          <t>project_status</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>CluePoints, Medidata CDS, No system (manual)</t>
+          <t>Planned, Active, On hold, Completed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>milestone_name</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Planned, Active, On hold, Completed</t>
+          <t>Protocol (v1), CTA submission, FPI, First SIV, LPI, interim DB lock cut-off, interim DB lock, final DB lock cut-off, final DB lock, Inspection</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>milestone_name</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Protocol (v1), CTA submission, FPI, First SIV, LPI, interim DB lock cut-off, interim DB lock, final DB lock cut-off, final DB lock, Inspection</t>
+          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>period_name_others</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
+          <t>Planning, Develop, Close</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>period_name_others</t>
+          <t>role_clinical</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Planning, Develop, Close</t>
+          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>role_others</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>role_others</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Project lead, Main staff, Other staff</t>
         </is>
@@ -5163,7 +5147,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>warning/information</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5515,17 +5499,17 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>A project's work_scope_type does not contradict its outsourcing_type. The two unambiguous ends are checked: 'Full outsourcing' against 'fully outsourced', and 'Full In-house' against 'fully in-housed'.</t>
+          <t>RETIRED at schema 7 (R-16). It reported a project whose work_scope_type contradicted its outsourcing_type.</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Warning - two columns on the same axis and only one of them drives the weights. A project marked 'Full In-house' and 'fully outsourced' is a slip, and the calculation would follow the field nobody was looking at. 'Partial outsourcing' is compatible with more than one scope and is not checked: a warning nobody can act on is a warning everybody learns to ignore.</t>
+          <t>Retired - the rule existed only because two columns sat on the same axis and one of them drove the weights. outsourcing_scope_det is free text now, so there is nothing left to contradict. A rule that can no longer fire is removed rather than left standing and unexplained; the id is not reused.</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5595,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.28</t>
+          <t>Application            app/PRAP.html v1.29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  7</t>
+          <t>Source schema version  8</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.30.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.31.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.4.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.5.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.9.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.10.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.11.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.12.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.3.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.4.xlsx</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1924,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>role_note</t>
+          <t>absorbed_by</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -3437,24 +3437,24 @@
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Basis for the factor.</t>
+          <t>If NOBODY holds this role on a project, which role picks the work up. Blank = the work is simply not counted. See the README.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>RoleFactor</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>role_note</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -3465,7 +3465,7 @@
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Unique key, e.g. PSN-001.</t>
+          <t>Basis for the factor.</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Display name.</t>
+          <t>Unique key, e.g. PSN-001.</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -3521,7 +3521,7 @@
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Grouping for the dashboard.</t>
+          <t>Display name.</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>primary_role</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -3549,7 +3549,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Usual role; an assignment can override it.</t>
+          <t>Grouping for the dashboard.</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>capacity_fte</t>
+          <t>primary_role</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -3577,7 +3577,7 @@
       <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
+          <t>Usual role; an assignment can override it.</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>employment_start</t>
+          <t>capacity_fte</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3605,7 +3605,7 @@
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Blank = open.</t>
+          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>employment_end</t>
+          <t>employment_start</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>employment_end</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -3661,7 +3661,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Blank = open.</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -3687,7 +3687,11 @@
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
-      <c r="F63" s="7" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -3697,7 +3701,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -3721,7 +3725,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>note_4</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -3745,7 +3749,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>note_5</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -3764,17 +3768,17 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3783,11 +3787,7 @@
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>Unique key. One row per person + project + role.</t>
-        </is>
-      </c>
+      <c r="F67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -3813,7 +3813,7 @@
       <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Foreign key to Person.</t>
+          <t>Unique key. One row per person + project + role.</t>
         </is>
       </c>
     </row>
@@ -3825,23 +3825,23 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>DERIVED - looked up from Person, do not type.</t>
+          <t>Foreign key to Person.</t>
         </is>
       </c>
     </row>
@@ -3853,23 +3853,23 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>DERIVED - looked up from Person, do not type.</t>
         </is>
       </c>
     </row>
@@ -3881,12 +3881,12 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3897,7 +3897,7 @@
       <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Must exist in RoleFactor for this project's type.</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>assign_start_date</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Date the person joins. BLANK = the project's own start date.</t>
+          <t>Must exist in RoleFactor for this project's type.</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>assign_end_date</t>
+          <t>assign_start_date</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -3953,7 +3953,7 @@
       <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Date the person leaves. BLANK = the project's own end date.</t>
+          <t>Date the person joins. BLANK = the project's own start date.</t>
         </is>
       </c>
     </row>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>person_weight</t>
+          <t>assign_end_date</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -3981,7 +3981,7 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>How much this person works on this project, e.g. 0.40.</t>
+          <t>Date the person leaves. BLANK = the project's own end date.</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>person_weight</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -4009,7 +4009,7 @@
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>How much this person works on this project, e.g. 0.40.</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -4035,7 +4035,11 @@
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="8" t="inlineStr"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -4045,7 +4049,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -4064,17 +4068,17 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -4083,11 +4087,7 @@
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr"/>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Foreign key to Assignment.</t>
-        </is>
-      </c>
+      <c r="F78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4113,7 +4113,7 @@
       <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Inclusive.</t>
+          <t>Foreign key to Assignment.</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -4141,7 +4141,7 @@
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Inclusive. Windows within one assignment must not overlap.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4153,12 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>weight_override</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4169,7 +4169,7 @@
       <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>REPLACES person_weight for these months - it does not multiply it.</t>
+          <t>Inclusive. Windows within one assignment must not overlap.</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>weight_override</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -4197,24 +4197,24 @@
       <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Why the weight differs.</t>
+          <t>REPLACES person_weight for these months - it does not multiply it.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>list_name</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4225,7 +4225,7 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Which list this value belongs to.</t>
+          <t>Why the weight differs.</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>list_name</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -4253,7 +4253,7 @@
       <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>A permitted value. Add a row inside the block to extend a list.</t>
+          <t>Which list this value belongs to.</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -4281,24 +4281,24 @@
       <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. when a value was added, or what it means.</t>
+          <t>A permitted value. Add a row inside the block to extend a list.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -4309,7 +4309,7 @@
       <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>Setting name.</t>
+          <t>Free text. e.g. when a value was added, or what it means.</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4337,7 +4337,7 @@
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Setting value.</t>
+          <t>Setting name.</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -4364,6 +4364,34 @@
       </c>
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Setting value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr"/>
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>What it controls.</t>
         </is>
@@ -4896,7 +4924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5532,6 +5560,72 @@
       <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Error - reported as itself rather than as a generic unknown value, because the remedy is a choice the file cannot make on the user's behalf. Only they know whether the trial ran in healthy volunteers or in patients, and guessing would put a wrong weight on real work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>V-27</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Every clinical trial's (project_type, clinical_phase, work_scope_type) has at least one row in PeriodWeightStandard - checked on the PROJECT, not on its periods.</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Error - V-19 is precise but only looks at periods a project actually has, so a project whose milestones are missing is never checked at all, and a combination that was never entered is reported once per period rather than once as the one thing that is wrong. This asks the blunter question first: is there any standard for this project at all. Without one, every period would be weighted 1.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>V-28</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Every role given to somebody on an assignment has at least one row in RoleFactor for that project's (project_type, clinical_phase, work_scope_type) - again independent of the project's periods.</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Error - V-03 checks the role against the type alone and V-23 against periods the project has, which leaves the same two gaps. The role would be calculated at factor 1.00 wherever it fell, and the project costed as though that role were free.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>V-29</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>A role that carries a factor, that nobody holds on the project, and that nothing covers for.</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Information - the direct consequence of REQ-CAL-16 and the reason it exists. Where an unstaffed role names somebody to cover, the figure is corrected; where it names nobody, the same under-estimate is still there and nothing else would say so. Information rather than a warning, because a project legitimately without a role is ordinary: this is a note about what the figures do NOT include, not a fault to correct.</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5595,7 +5689,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -5698,13 +5792,28 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>split_shared_role_fte</t>
+          <t>absorb_unstaffed_role_factor</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1 = where nobody holds a role on a project, its factor is added to the role named in RoleFactor.absorbed_by, because the work still has to be done by whoever is there. 0 = an unstaffed role simply costs nothing, which is how versions before this one behaved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>split_shared_role_fte</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>1 = when several people hold the same role on one project in a month, the role factor is divided between them. 0 = each is charged the whole factor, which is how versions before this one behaved.</t>
         </is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.29</t>
+          <t>Application            app/PRAP.html v1.30</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.31.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.32.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.5.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.6.xlsx</t>
         </is>
       </c>
     </row>
@@ -5593,17 +5593,17 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Every role given to somebody on an assignment has at least one row in RoleFactor for that project's (project_type, clinical_phase, work_scope_type) - again independent of the project's periods.</t>
+          <t>RETIRED at v2.32 (R-18), one version after it was added. It reported an assignment whose role had no RoleFactor row for that project's (project_type, clinical_phase, work_scope_type) at all.</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Error - V-03 checks the role against the type alone and V-23 against periods the project has, which leaves the same two gaps. The role would be calculated at factor 1.00 wherever it fell, and the project costed as though that role were free.</t>
+          <t>Retired - and deliberately not reinstated at a lower severity. What the rule SAID was true; what it did not account for was WHEN it said it. An error refuses the edit that raised it (REQ-IMP-09), and unlike V-23 this one did not need the project to have any periods - so it fired on a project still being built, which is exactly when assignments are being typed in. A user could not record who was on a project until the standing assumptions carried a factor for their role, which is backwards: the plan is the document being written, the assumptions are maintained separately. The gap is not denied - V-03 still refuses a role invalid for the project type, and V-23 still reports a role with no factor for a period the project spans, which is the same finding at the point where it can be acted on. The id is not reused.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.30</t>
+          <t>Application            app/PRAP.html v1.31</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-26</t>
+          <t>Generated              2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.32.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.33.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.6.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.7.xlsx</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Every Assignment.role_name appears in RoleFactor for that project's type.</t>
+          <t>Every Assignment.role_name appears in RoleFactor for that project's type - the coarse half of the question V-23 asks precisely.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Error - row rejected. Was a warning in v0.1; roles are now type-specific, so a mismatch is a real error.</t>
+          <t>Error, REPORTED BUT NEVER REFUSING THE ROW (R-19). Was a warning in v0.1; roles are now type-specific, so a mismatch is a real error and the figures for that role are wrong. It is still not a reason to refuse the row: RoleFactor is a standing document maintained separately from any one plan, and the person really is on the project whether or not somebody has entered a factor for their role yet. Kept alongside V-23 because it catches a mistyped role name at once, where V-23 only speaks once the assignment reaches a period and draws FTE.</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>For every (project_type, clinical_phase, period_name, role_name) an assignment can actually reach, a RoleFactor row exists.</t>
+          <t>Every (project_type, clinical_phase, work_scope_type, period_name, role_name) that a PERSON-MONTH ACTUALLY LOOKED UP has a RoleFactor row. Raised BY the calculation (R-19), grouped on that whole composition, and counted in person-months affected.</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Error - a factor missing for ONE period of a project silently drops that stretch to 1.00, which is a wrong number rather than an obvious gap. Checked against the periods each assignment spans, not against the whole cross-product.</t>
+          <t>Error - a factor missing for one period silently drops that stretch to 1.00, which is a wrong number rather than an obvious gap. Two things changed at R-19. It is keyed on the composition the lookup uses, and reported only where a figure was actually produced - asked off the sheets it walked every period of every project an assignment belonged to, so it demanded rows for periods nobody was ever booked into. And because it exists only after the arithmetic, it CANNOT REFUSE AN EDIT: it says the figures are short of an assumption, not that the row is wrong.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.31</t>
+          <t>Application            app/PRAP.html v1.32</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.33.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.34.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.7.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.8.xlsx</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Error, REPORTED BUT NEVER REFUSING THE ROW (R-19). Was a warning in v0.1; roles are now type-specific, so a mismatch is a real error and the figures for that role are wrong. It is still not a reason to refuse the row: RoleFactor is a standing document maintained separately from any one plan, and the person really is on the project whether or not somebody has entered a factor for their role yet. Kept alongside V-23 because it catches a mistyped role name at once, where V-23 only speaks once the assignment reaches a period and draws FTE.</t>
+          <t>Error, CLASS CONDITIONAL (R-25): reported at full severity, never refusing the row, and named at Save so the user can keep it knowingly. Was a warning in v0.1; roles are now type-specific, so a mismatch is a real error and the figures for that role are wrong. It is still not a reason to refuse the row: RoleFactor is a standing document maintained separately from any one plan, and the person really is on the project whether or not somebody has entered a factor for their role yet. Kept alongside V-23 because it catches a mistyped role name at once, where V-23 only speaks once the assignment reaches a period and draws FTE.</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Error - a factor missing for one period silently drops that stretch to 1.00, which is a wrong number rather than an obvious gap. Two things changed at R-19. It is keyed on the composition the lookup uses, and reported only where a figure was actually produced - asked off the sheets it walked every period of every project an assignment belonged to, so it demanded rows for periods nobody was ever booked into. And because it exists only after the arithmetic, it CANNOT REFUSE AN EDIT: it says the figures are short of an assumption, not that the row is wrong.</t>
+          <t>Error, CLASS CONDITIONAL (R-25) - a factor missing for one period silently drops that stretch to 1.00, which is a wrong number rather than an obvious gap. Two things changed at R-19. It is keyed on the composition the lookup uses, and reported only where a figure was actually produced - asked off the sheets it walked every period of every project an assignment belonged to, so it demanded rows for periods nobody was ever booked into. And because it exists only after the arithmetic, it CANNOT REFUSE AN EDIT: it says the figures are short of an assumption, not that the row is wrong.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.32</t>
+          <t>Application            app/PRAP.html v1.33</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.34.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.35.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.8.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.9.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.10.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.11.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.12.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.13.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.4.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.5.xlsx</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5626,6 +5626,28 @@
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Information - the direct consequence of REQ-CAL-16 and the reason it exists. Where an unstaffed role names somebody to cover, the figure is corrected; where it names nobody, the same under-estimate is still there and nothing else would say so. Information rather than a warning, because a project legitimately without a role is ordinary: this is a note about what the figures do NOT include, not a fault to correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>V-30</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Config has no row for a setting the application reads, so its built-in default is in force. Reported for every such setting, naming the value being used.</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Information - the file is not malformed and the application is doing the only sensible thing with it, so this is a note rather than a fault. It exists because the absence is otherwise INVISIBLE: every setting is read through a fallback, and the delivered values equal the defaults, so on a stock file nothing moves. A plan whose under-allocation floor had been set to 0.80, or whose shared-role division had been turned off to compare with last year, would revert the moment its row went missing - every dependent figure changing, and nothing on screen saying why. Since v2.35 the row cannot be DELETED in the application (the Config table offers neither '+ row' nor 'Delete', because each setting is read by name), so this now reports a hand-edited workbook or one from a version that predates the setting.</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5807,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Display unit: 'FTE' or 'percent'.</t>
+          <t>Display unit for the figures on screen. 'FTE' shows a WEIGHT: 1.00 is one person working a full month on the project and 0.50 is half of one, so ordinary values run about 0.1 to 1.0. 'hours' shows that same weight multiplied by fte_hours_per_month. Display only - it changes nothing that is stored, and no figure the calculation produces.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.33</t>
+          <t>Application            app/PRAP.html v1.34</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-27</t>
+          <t>Generated              2026-08-28</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.35.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.36.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.9.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.10.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.34</t>
+          <t>Application            app/PRAP.html v1.35</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.36.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.37.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.10.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.11.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.35</t>
+          <t>Application            app/PRAP.html v1.36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  8</t>
+          <t>Source schema version  9</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-28</t>
+          <t>Generated              2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.37.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.38.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.11.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.12.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.11.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.12.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.13.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.14.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.5.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.6.xlsx</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1853,60 +1853,90 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
+          <t>Project|Assignment</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>scope, ref_id, month</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>list_name, value</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F13" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>list_name, value</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>settings</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F15" s="7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1924,7 +1954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2565,7 +2595,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>estimation_type</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -2581,7 +2611,7 @@
       <c r="E24" s="8" t="inlineStr"/>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>'automatic' (default) or 'manual'. Manual means the monthly FTE for THIS PROJECT is stated on MonthlyEstimate rather than calculated, and the people assigned that month are scaled to add up to it.</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -2607,7 +2637,11 @@
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -2617,7 +2651,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -2641,7 +2675,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>note_4</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -2665,7 +2699,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>note_5</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -2684,17 +2718,17 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Project</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -2703,11 +2737,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Foreign key to Project.</t>
-        </is>
-      </c>
+      <c r="F29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -2717,23 +2747,23 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>project_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>DERIVED - looked up from Project, do not type.</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -2745,27 +2775,23 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>milestone_name</t>
+          <t>project_name</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>milestone_name</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr"/>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>From the standard list of ten. 'Inspection' may appear on several rows.</t>
+          <t>DERIVED - looked up from Project, do not type.</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2803,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>milestone_date</t>
+          <t>milestone_name</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2790,10 +2816,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr"/>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>milestone_name</t>
+        </is>
+      </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Planned date.</t>
+          <t>From the standard list of ten. 'Inspection' may appear on several rows.</t>
         </is>
       </c>
     </row>
@@ -2805,12 +2835,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>milestone_seq</t>
+          <t>milestone_date</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -2821,7 +2851,7 @@
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Display order on the timeline.</t>
+          <t>Planned date.</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2863,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>milestone_seq</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -2849,24 +2879,24 @@
       <c r="E34" s="8" t="inlineStr"/>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. why a date moved, or which inspection body.</t>
+          <t>Display order on the timeline.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>ProjectPeriod</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -2877,7 +2907,7 @@
       <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>Free text. e.g. why a date moved, or which inspection body.</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2919,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -2905,7 +2935,7 @@
       <c r="E36" s="8" t="inlineStr"/>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>From the set for this project's type. UNIQUE within a project, so (project_id, period_name) is the key (R-11).</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2947,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>period_seq</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -2933,7 +2963,7 @@
       <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Orders periods along the timeline. Unique within a project.</t>
+          <t>From the set for this project's type. UNIQUE within a project, so (project_id, period_name) is the key (R-11).</t>
         </is>
       </c>
     </row>
@@ -2945,12 +2975,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>period_seq</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2961,7 +2991,7 @@
       <c r="E38" s="8" t="inlineStr"/>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Inclusive.</t>
+          <t>Orders periods along the timeline. Unique within a project.</t>
         </is>
       </c>
     </row>
@@ -2973,7 +3003,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -2989,7 +3019,7 @@
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Inclusive. Periods must not overlap or leave a gap.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3031,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -3017,7 +3047,7 @@
       <c r="E40" s="8" t="inlineStr"/>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Effort multiplier. Clinical trial types: seeded from PeriodWeightStandard. Others: type it.</t>
+          <t>Inclusive. Periods must not overlap or leave a gap.</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3059,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -3045,24 +3075,24 @@
       <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. why a derived date was overridden by hand.</t>
+          <t>Effort multiplier. Clinical trial types: seeded from PeriodWeightStandard. Others: type it.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>ProjectPeriod</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -3070,14 +3100,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
+      <c r="E42" s="8" t="inlineStr"/>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>A clinical trial type. 'Others' projects take manual weights instead.</t>
+          <t>Free text. e.g. why a derived date was overridden by hand.</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3115,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -3104,12 +3130,12 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>The phase this standard applies to.</t>
+          <t>A clinical trial type. 'Others' projects take manual weights instead.</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3147,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -3136,12 +3162,12 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>The work scope this standard applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
+          <t>The phase this standard applies to.</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3179,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -3168,12 +3194,12 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>One of the seven clinical periods. Unique within a project (R-11).</t>
+          <t>The work scope this standard applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3211,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3198,10 +3224,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr"/>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>period_name_clinical</t>
+        </is>
+      </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. Default multiplier for this phase and period.</t>
+          <t>One of the seven clinical periods. Unique within a project (R-11).</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3243,12 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -3229,24 +3259,24 @@
       <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. the basis for this weight.</t>
+          <t>YOU SUPPLY. Default multiplier for this phase and period.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>RoleFactor</t>
+          <t>PeriodWeightStandard</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3254,14 +3284,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
+      <c r="E48" s="8" t="inlineStr"/>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Which type's role list this row belongs to.</t>
+          <t>Free text. e.g. the basis for this weight.</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3299,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -3288,12 +3314,12 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>The phase this factor applies to. Leave EMPTY for 'Others'.</t>
+          <t>Which type's role list this row belongs to.</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3331,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -3320,12 +3346,12 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>The work scope this factor applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
+          <t>The phase this factor applies to. Leave EMPTY for 'Others'.</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3363,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -3350,10 +3376,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>work_scope_type</t>
+        </is>
+      </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>The period this factor applies to.</t>
+          <t>The work scope this factor applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3395,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -3381,7 +3411,7 @@
       <c r="E52" s="8" t="inlineStr"/>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>The role.</t>
+          <t>The period this factor applies to.</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3423,12 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>role_factor</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -3409,7 +3439,7 @@
       <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. Relative burden of this role in this period.</t>
+          <t>The role.</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3451,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>absorbed_by</t>
+          <t>role_factor</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3437,7 +3467,7 @@
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>If NOBODY holds this role on a project, which role picks the work up. Blank = the work is simply not counted. See the README.</t>
+          <t>YOU SUPPLY. Relative burden of this role in this period.</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3479,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>role_note</t>
+          <t>absorbed_by</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -3465,24 +3495,24 @@
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Basis for the factor.</t>
+          <t>If NOBODY holds this role on a project, which role picks the work up. Blank = the work is simply not counted. See the README.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>RoleFactor</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>role_note</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3493,7 +3523,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Unique key, e.g. PSN-001.</t>
+          <t>Basis for the factor.</t>
         </is>
       </c>
     </row>
@@ -3505,12 +3535,12 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -3521,7 +3551,7 @@
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Display name.</t>
+          <t>Unique key, e.g. PSN-001.</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3563,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -3549,7 +3579,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Grouping for the dashboard.</t>
+          <t>Display name.</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3591,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>primary_role</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -3577,7 +3607,7 @@
       <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Usual role; an assignment can override it.</t>
+          <t>Grouping for the dashboard.</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3619,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>capacity_fte</t>
+          <t>primary_role</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -3605,7 +3635,7 @@
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
+          <t>Usual role; an assignment can override it.</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3647,12 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>employment_start</t>
+          <t>capacity_fte</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -3633,7 +3663,7 @@
       <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Blank = open.</t>
+          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3675,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>employment_end</t>
+          <t>employment_start</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -3673,12 +3703,12 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>employment_end</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3689,7 +3719,7 @@
       <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Blank = open.</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3731,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -3715,7 +3745,11 @@
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr"/>
-      <c r="F64" s="8" t="inlineStr"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -3725,7 +3759,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -3749,7 +3783,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>note_4</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -3773,7 +3807,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>note_5</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -3792,17 +3826,17 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -3811,11 +3845,7 @@
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>Unique key. One row per person + project + role.</t>
-        </is>
-      </c>
+      <c r="F68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -3825,7 +3855,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -3841,7 +3871,7 @@
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Foreign key to Person.</t>
+          <t>Unique key. One row per person + project + role.</t>
         </is>
       </c>
     </row>
@@ -3853,23 +3883,23 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>DERIVED - looked up from Person, do not type.</t>
+          <t>Foreign key to Person.</t>
         </is>
       </c>
     </row>
@@ -3881,23 +3911,23 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>DERIVED - looked up from Person, do not type.</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3939,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3925,7 +3955,7 @@
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Must exist in RoleFactor for this project's type.</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3967,12 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>assign_start_date</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3953,7 +3983,7 @@
       <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Date the person joins. BLANK = the project's own start date.</t>
+          <t>Must exist in RoleFactor for this project's type.</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3995,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>assign_end_date</t>
+          <t>assign_start_date</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -3981,7 +4011,7 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>Date the person leaves. BLANK = the project's own end date.</t>
+          <t>Date the person joins. BLANK = the project's own start date.</t>
         </is>
       </c>
     </row>
@@ -3993,12 +4023,12 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>person_weight</t>
+          <t>assign_end_date</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4009,7 +4039,7 @@
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>How much this person works on this project, e.g. 0.40.</t>
+          <t>Date the person leaves. BLANK = the project's own end date.</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4051,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>person_weight</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -4037,7 +4067,7 @@
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>How much this person works on this project, e.g. 0.40.</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4079,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>estimation_type</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -4063,7 +4093,11 @@
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr"/>
-      <c r="F77" s="7" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>'automatic' (default) or 'manual'. Manual means the monthly FTE for THIS ASSIGNMENT is stated on MonthlyEstimate rather than calculated.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -4073,7 +4107,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -4087,22 +4121,26 @@
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr"/>
-      <c r="F78" s="8" t="inlineStr"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4111,26 +4149,22 @@
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>Foreign key to Assignment.</t>
-        </is>
-      </c>
+      <c r="F79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -4139,11 +4173,7 @@
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr"/>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>Inclusive.</t>
-        </is>
-      </c>
+      <c r="F80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -4153,12 +4183,12 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4169,7 +4199,7 @@
       <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Inclusive. Windows within one assignment must not overlap.</t>
+          <t>Foreign key to Assignment.</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4211,12 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>weight_override</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -4197,7 +4227,7 @@
       <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>REPLACES person_weight for these months - it does not multiply it.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
@@ -4209,12 +4239,12 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4225,24 +4255,24 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Why the weight differs.</t>
+          <t>Inclusive. Windows within one assignment must not overlap.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>list_name</t>
+          <t>weight_override</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -4253,19 +4283,19 @@
       <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Which list this value belongs to.</t>
+          <t>REPLACES person_weight for these months - it does not multiply it.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -4281,24 +4311,24 @@
       <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>A permitted value. Add a row inside the block to extend a list.</t>
+          <t>Why the weight differs.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -4309,24 +4339,24 @@
       <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. when a value was added, or what it means.</t>
+          <t>'project' or 'assignment' - which of the two this figure is for.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>ref_id</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4337,19 +4367,19 @@
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Setting name.</t>
+          <t>The project_id or assignment_id it belongs to, per scope.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -4365,19 +4395,19 @@
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Setting value.</t>
+          <t>The month, as YYYY-MM.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>fte</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -4392,6 +4422,230 @@
       </c>
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>The monthly FTE, STATED rather than calculated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>MonthlyEstimate</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>edited_at</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>When it was last set. The application fills this in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>MonthlyEstimate</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>note_1</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Why this figure was stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Which list this value belongs to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>A permitted value. Add a row inside the block to extend a list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>note_1</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr"/>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Free text. e.g. when a value was added, or what it means.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Setting name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr"/>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Setting value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr"/>
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>What it controls.</t>
         </is>
@@ -4924,7 +5178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5648,6 +5902,50 @@
       <c r="D35" s="7" t="inlineStr">
         <is>
           <t>Information - the file is not malformed and the application is doing the only sensible thing with it, so this is a note rather than a fault. It exists because the absence is otherwise INVISIBLE: every setting is read through a fallback, and the delivered values equal the defaults, so on a stock file nothing moves. A plan whose under-allocation floor had been set to 0.80, or whose shared-role division had been turned off to compare with last year, would revert the moment its row went missing - every dependent figure changing, and nothing on screen saying why. Since v2.35 the row cannot be DELETED in the application (the Config table offers neither '+ row' nor 'Delete', because each setting is read by name), so this now reports a hand-edited workbook or one from a version that predates the setting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>V-31</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>A project or assignment set to MANUAL has months it covers that carry no MonthlyEstimate figure. Named, with the months listed.</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Error - those months are counted as 0.00, and a figure silently dropping to zero is the one outcome this feature must never produce quietly. Not a refusal: it is raised from the CALCULATION, like V-23, because it is something that happened to a number rather than a fact about a sheet, and a finding that exists only after the arithmetic cannot refuse the edit that led to it. Switching to manual copies every month across, so a month with no figure is one that has since been removed or a month the thing has grown into - the application offers to fill them from the calculation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>V-32</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>A project set to MANUAL has a figure for a month in which nobody is assigned to it.</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Error - the figure is NOT applied. A project month is shared out among the people on it, so there is nobody to give this to; applying it anyway would give the project a total that none of its people account for, which is exactly the disagreement REQ-CAL-18 scales the people to avoid. Assign somebody to those months, or remove the figure.</t>
         </is>
       </c>
     </row>
@@ -5711,7 +6009,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-08-30</t>
+          <t>Generated              2026-09-02</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.36</t>
+          <t>Application            app/PRAP.html v1.37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  9</t>
+          <t>Source schema version  10</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.38.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.39.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.12.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.13.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.12.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.13.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.14.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.15.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.6.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.7.xlsx</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>standard_fte</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -3259,7 +3259,7 @@
       <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. Default multiplier for this phase and period.</t>
+          <t>YOU SUPPLY. The STANDARD MONTHLY FTE a project of this type, phase and scope takes in this period - a magnitude, not a multiplier. 4.02 means the period costs about four full-time people a month. The project's own ProjectPeriod.weight then adjusts it up or down for that particular study, and the role factors divide it between the roles staffed.</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-02</t>
+          <t>Generated              2026-09-03</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Effort multiplier. Clinical trial types: seeded from PeriodWeightStandard. Others: type it.</t>
+          <t>THIS PROJECT'S OWN ADJUSTMENT to the standard for its type, phase and scope (REQ-CAL-19). 1.00 means an ordinary project of its kind; 1.20 means this one takes a fifth more. It does NOT carry the magnitude - PeriodWeightStandard.standard_fte does.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.37</t>
+          <t>Application            app/PRAP.html v1.38</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.39.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.40.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.13.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.14.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-03</t>
+          <t>Generated              2026-09-04</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.38</t>
+          <t>Application            app/PRAP.html v1.39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  10</t>
+          <t>Source schema version  11</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Check the reference tables FIRST: python tools/prap_io.py to-json &lt;file.xlsx&gt; -o plan.prap.json, then look at PeriodWeightStandard and RoleFactor. A plan started blank seeds every one of them at 1.00 with a note saying so.</t>
+          <t>Check the reference tables FIRST: python tools/prap_io.py to-json &lt;file.xlsx&gt; -o plan.prap.json, then look at PeriodFTEStandard and RoleFactor. A plan started blank seeds every one of them at 1.00 with a note saying so.</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>The Lists and Config sheets of the delivered template, plus a complete PeriodWeightStandard and RoleFactor grid built from those lists - every (type, phase, period) and (type, phase, period, role) combination, so nothing silently falls back to 1.00 and V-23 never fires.</t>
+          <t>The Lists and Config sheets of the delivered template, plus a complete PeriodFTEStandard and RoleFactor grid built from those lists - every (type, phase, period) and (type, phase, period, role) combination, so nothing silently falls back to 1.00 and V-23 never fires.</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.40.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.41.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.14.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.15.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.13.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.14.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.15.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.16.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.7.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.8.xlsx</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -3075,7 +3075,7 @@
       <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>THIS PROJECT'S OWN ADJUSTMENT to the standard for its type, phase and scope (REQ-CAL-19). 1.00 means an ordinary project of its kind; 1.20 means this one takes a fifth more. It does NOT carry the magnitude - PeriodWeightStandard.standard_fte does.</t>
+          <t>THIS PROJECT'S OWN ADJUSTMENT to the standard for its type, phase and scope (REQ-CAL-19). 1.00 means an ordinary project of its kind; 1.20 means this one takes a fifth more. It does NOT carry the magnitude - PeriodFTEStandard.standard_fte does.</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>PeriodWeightStandard</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>A clinical trial carries a clinical_phase, and PeriodWeightStandard has rows for that phase. Not applied to 'Others' projects, whose weights are entered directly.</t>
+          <t>A clinical trial carries a clinical_phase, and PeriodFTEStandard has rows for that phase. Not applied to 'Others' projects, whose weights are entered directly.</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Every clinical trial's (project_type, clinical_phase, work_scope_type) has at least one row in PeriodWeightStandard - checked on the PROJECT, not on its periods.</t>
+          <t>Every clinical trial's (project_type, clinical_phase, work_scope_type) has at least one row in PeriodFTEStandard - checked on the PROJECT, not on its periods.</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.39</t>
+          <t>Application            app/PRAP.html v1.40</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.15.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.16.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.41.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.42.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.40</t>
+          <t>Application            app/PRAP.html v1.41</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.42.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.43.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.16.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.17.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.41</t>
+          <t>Application            app/PRAP.html v1.42</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.43.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.44.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.17.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.18.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.42</t>
+          <t>Application            app/PRAP.html v1.43</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-04</t>
+          <t>Generated              2026-09-05</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.44.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.45.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.18.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.19.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.43</t>
+          <t>Application            app/PRAP.html v1.44</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.45.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.46.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.19.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.20.xlsx</t>
         </is>
       </c>
     </row>
